--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104549_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104549_W11.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0974</v>
+        <v>5.0373</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6013</v>
+        <v>6.1581</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5039</v>
+        <v>-1.1208</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0269</v>
+        <v>4.0278</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8008</v>
+        <v>2.8003</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2262</v>
+        <v>1.2275</v>
       </c>
       <c r="J2" t="n">
-        <v>7.7789</v>
+        <v>7.7496</v>
       </c>
       <c r="K2" t="n">
-        <v>3.117</v>
+        <v>3.1026</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6619</v>
+        <v>4.6469</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.752</v>
+        <v>-3.7218</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.4357</v>
+        <v>-3.4194</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3239</v>
+        <v>0.2568</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0434</v>
+        <v>-0.4533</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3673</v>
+        <v>0.7101</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6013</v>
+        <v>4.609</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1687</v>
+        <v>6.5447</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5675</v>
+        <v>-1.9357</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0393</v>
+        <v>5.096</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0606</v>
+        <v>3.7516</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0213</v>
+        <v>1.3445</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3446</v>
+        <v>6.7415</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1083</v>
+        <v>4.0539</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2363</v>
+        <v>2.6876</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3053</v>
+        <v>-1.6455</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0477</v>
+        <v>-0.3023</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.2576</v>
+        <v>-1.3432</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2671</v>
+        <v>-0.6935</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6635</v>
+        <v>-0.8993</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6037</v>
+        <v>0.2058</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8723</v>
+        <v>3.1215</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2479</v>
+        <v>3.8565</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3756</v>
+        <v>-0.735</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1227</v>
+        <v>1.0406</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7634</v>
+        <v>1.0598</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3593</v>
+        <v>-0.0193</v>
       </c>
       <c r="J4" t="n">
-        <v>6.7929</v>
+        <v>3.3297</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0796</v>
+        <v>1.1032</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7133</v>
+        <v>2.2265</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6702</v>
+        <v>-2.2891</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3162</v>
+        <v>-0.0433</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.354</v>
+        <v>-2.2458</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4526</v>
+        <v>0.785</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2521</v>
+        <v>0.369</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2005</v>
+        <v>0.416</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9438</v>
+        <v>2.0992</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8625</v>
+        <v>2.8322</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9187</v>
+        <v>-0.7331</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.3042</v>
+        <v>-3.3074</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.841</v>
+        <v>-3.8418</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4367</v>
+        <v>-0.4591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6163</v>
+        <v>0.6065</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8675</v>
+        <v>-2.8483</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.788</v>
+        <v>-2.7761</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3161</v>
+        <v>0.4749</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0212</v>
+        <v>0.0229</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2949</v>
+        <v>0.452</v>
       </c>
       <c r="V5" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W5" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6512</v>
+        <v>1.5857</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9891</v>
+        <v>1.9772</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3379</v>
+        <v>-0.3915</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0952</v>
+        <v>2.0943</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2294</v>
+        <v>0.2325</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2624</v>
+        <v>3.2547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9853</v>
+        <v>2.9789</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1672</v>
+        <v>-1.1604</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0097</v>
+        <v>-0.0534</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2033</v>
+        <v>0.6139</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6191</v>
+        <v>-1.3519</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8224</v>
+        <v>1.9658</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4064</v>
+        <v>-1.4139</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4384</v>
+        <v>-1.4498</v>
       </c>
       <c r="I7" t="n">
-        <v>0.032</v>
+        <v>0.0359</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5242</v>
+        <v>-1.5445</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6735</v>
+        <v>-1.6934</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1178</v>
+        <v>0.1306</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0634</v>
+        <v>0.483</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9467</v>
+        <v>0.2413</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1167</v>
+        <v>0.2418</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2578</v>
+        <v>-2.252</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4773</v>
+        <v>0.548</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.7351</v>
+        <v>-2.7999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6857</v>
+        <v>-0.7744</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0837</v>
+        <v>-0.2814</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6019</v>
+        <v>-0.4931</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1978</v>
+        <v>0.7712</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1456</v>
+        <v>-0.3382</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3434</v>
+        <v>1.1094</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8834</v>
+        <v>-1.5457</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0619</v>
+        <v>0.0568</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.9453</v>
+        <v>-1.6025</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5205</v>
+        <v>-0.4367</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1603</v>
+        <v>-0.2232</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3602</v>
+        <v>-0.2135</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3461</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.982</v>
+        <v>-2.3908</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0953</v>
+        <v>1.3416</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0772</v>
+        <v>-3.7324</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.773</v>
+        <v>-1.6741</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2799</v>
+        <v>-0.0806</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4931</v>
+        <v>-1.5935</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7909</v>
+        <v>1.1886</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3259</v>
+        <v>-0.1519</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1168</v>
+        <v>1.3405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5639</v>
+        <v>-2.8628</v>
       </c>
       <c r="N9" t="n">
-        <v>0.046</v>
+        <v>0.0713</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6099</v>
+        <v>-2.934</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1578</v>
+        <v>0.3728</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6956</v>
+        <v>0.0439</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4621</v>
+        <v>0.3289</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7655</v>
+        <v>-3.3431</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5963</v>
+        <v>-4.2621</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8308</v>
+        <v>0.9191</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7509</v>
+        <v>-4.7505</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3203</v>
+        <v>-1.3184</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4305</v>
+        <v>-3.4321</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.3442</v>
+        <v>-3.3628</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2091</v>
+        <v>-1.2173</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1352</v>
+        <v>-2.1455</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4066</v>
+        <v>-1.3877</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8293</v>
+        <v>-0.4136</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2521</v>
+        <v>-0.8993</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4228</v>
+        <v>0.4857</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4238</v>
+        <v>-5.5128</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2611</v>
+        <v>-2.1598</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1627</v>
+        <v>-3.353</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9915</v>
+        <v>-3.9809</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8383</v>
+        <v>-0.8414</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1532</v>
+        <v>-3.1395</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3618</v>
+        <v>-0.3734</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5857</v>
+        <v>-0.5968</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6298</v>
+        <v>-3.6075</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.3771</v>
+        <v>-3.3629</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7945</v>
+        <v>0.6957</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369</v>
+        <v>0.4899</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4255</v>
+        <v>0.2058</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9782</v>
+        <v>-6.5915</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1397</v>
+        <v>-4.9333</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8385</v>
+        <v>-1.6582</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.0906</v>
+        <v>-6.0954</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2465</v>
+        <v>-3.2564</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8441</v>
+        <v>-2.839</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.823</v>
+        <v>-2.8471</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0415</v>
+        <v>-3.0551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2675</v>
+        <v>-3.2483</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.0626</v>
+        <v>-3.0471</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2465</v>
+        <v>0.6421</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0484</v>
+        <v>0.1901</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2949</v>
+        <v>0.452</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.037999999999999</v>
+        <v>-3.023599999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>10.8259</v>
+        <v>10.5512</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.8639</v>
+        <v>-13.5747</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.7182</v>
+        <v>-9.7379</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1839</v>
+        <v>1.1505</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.9018</v>
+        <v>-10.8886</v>
       </c>
       <c r="J13" t="n">
-        <v>14.6776</v>
+        <v>14.4484</v>
       </c>
       <c r="K13" t="n">
-        <v>2.216999999999999</v>
+        <v>2.089299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>12.4605</v>
+        <v>12.3591</v>
       </c>
       <c r="M13" t="n">
-        <v>-24.3956</v>
+        <v>-24.1865</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0332</v>
+        <v>-0.9384999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-23.3623</v>
+        <v>-23.2477</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6709</v>
+        <v>5.690899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7444</v>
+        <v>14.7964</v>
       </c>
       <c r="S13" t="n">
-        <v>2.102</v>
+        <v>2.1131</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.27</v>
+        <v>-1.2574</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3722</v>
+        <v>3.3706</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.089399999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4919</v>
+        <v>6.465400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.584499999999999</v>
+        <v>-7.5549</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.071099999999999</v>
+        <v>8.7004</v>
       </c>
       <c r="E14" t="n">
-        <v>8.763400000000001</v>
+        <v>8.958399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6924</v>
+        <v>-0.258</v>
       </c>
       <c r="G14" t="n">
-        <v>9.1645</v>
+        <v>9.1599</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6149</v>
+        <v>8.6004</v>
       </c>
       <c r="J14" t="n">
-        <v>10.1579</v>
+        <v>10.1304</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3463</v>
+        <v>0.3447</v>
       </c>
       <c r="L14" t="n">
-        <v>9.8116</v>
+        <v>9.785600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9935</v>
+        <v>-0.9704</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4375</v>
+        <v>-0.7978</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6723</v>
+        <v>-0.268</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6753</v>
+        <v>2.4323</v>
       </c>
       <c r="E15" t="n">
-        <v>1.867</v>
+        <v>1.387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8083</v>
+        <v>1.0453</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9036</v>
+        <v>1.9083</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2555</v>
+        <v>-0.2502</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1591</v>
+        <v>2.1584</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4285</v>
+        <v>1.4197</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4747</v>
+        <v>-0.4794</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4751</v>
+        <v>0.4886</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2017</v>
+        <v>-0.4564</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4386</v>
+        <v>-0.0327</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6403</v>
+        <v>-0.4237</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2006</v>
+        <v>2.0762</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3219</v>
+        <v>1.4171</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8787</v>
+        <v>0.6591</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8024</v>
+        <v>1.8069</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1834</v>
+        <v>-0.1756</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9858</v>
+        <v>1.9825</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7509</v>
+        <v>1.7312</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1216</v>
+        <v>2.1072</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0515</v>
+        <v>0.0757</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.196</v>
+        <v>0.0629</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5898</v>
+        <v>-0.4718</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7857</v>
+        <v>0.5347</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7898</v>
+        <v>2.0647</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1852</v>
+        <v>3.2728</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3955</v>
+        <v>-1.2081</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0499</v>
+        <v>1.0505</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.485</v>
+        <v>-1.474</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5348</v>
+        <v>2.5244</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9091</v>
+        <v>2.8827</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L17" t="n">
-        <v>3.5743</v>
+        <v>3.5517</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8593</v>
+        <v>-1.8323</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4189</v>
+        <v>-0.1451</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5898</v>
+        <v>-0.4718</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1709</v>
+        <v>0.3267</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.507</v>
+        <v>1.5574</v>
       </c>
       <c r="E18" t="n">
-        <v>2.579</v>
+        <v>2.6594</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.072</v>
+        <v>-1.102</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0618</v>
+        <v>3.0556</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1661</v>
+        <v>-0.1584</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2278</v>
+        <v>3.214</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5479</v>
+        <v>4.5155</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2087</v>
+        <v>4.1848</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4861</v>
+        <v>-1.4599</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2353</v>
+        <v>-0.1811</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6079</v>
+        <v>-0.4904</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3726</v>
+        <v>0.3093</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7018</v>
+        <v>0.9691</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0407</v>
+        <v>1.2615</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3389</v>
+        <v>-0.2924</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6651</v>
+        <v>0.669</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7623</v>
+        <v>-0.7627</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2031</v>
+        <v>1.1942</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6317</v>
+        <v>0.6254</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3003</v>
+        <v>-1.2879</v>
       </c>
       <c r="N19" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0668</v>
+        <v>0.2009</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.121</v>
+        <v>0.116</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4571</v>
+        <v>-0.0638</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8788</v>
+        <v>-1.139</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3359</v>
+        <v>1.0752</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8539</v>
+        <v>-0.8452</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2164</v>
+        <v>-1.215</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3626</v>
+        <v>0.3697</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4813</v>
+        <v>-0.4905</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9702</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3726</v>
+        <v>-0.3548</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>1.031</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4567</v>
+        <v>0.2228</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5743</v>
+        <v>0.2919</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4972</v>
+        <v>-0.9002</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2931</v>
+        <v>2.9254</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7903</v>
+        <v>-3.8257</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5151</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2063</v>
+        <v>2.2031</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7214</v>
+        <v>-2.7106</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2024</v>
+        <v>3.1882</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9785</v>
+        <v>2.9647</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.7175</v>
+        <v>-3.6957</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9453</v>
+        <v>-2.934</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6569</v>
+        <v>0.2415</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3176</v>
+        <v>-0.0351</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3393</v>
+        <v>0.2766</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9676</v>
+        <v>-0.964</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1018</v>
+        <v>-0.1022</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7408</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7781</v>
+        <v>-0.7736</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.423</v>
+        <v>-4.8478</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9048</v>
+        <v>-2.7386</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5182</v>
+        <v>-2.1092</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7194</v>
+        <v>-1.7412</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6049</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3243</v>
+        <v>-2.3253</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5876</v>
+        <v>0.5344</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9688</v>
+        <v>0.9298</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3813</v>
+        <v>-0.3954</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.307</v>
+        <v>-2.2756</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3011</v>
+        <v>-0.6922</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9557</v>
+        <v>-0.7204</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3454</v>
+        <v>0.0283</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4768</v>
+        <v>-8.0007</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3011</v>
+        <v>-4.3272</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1757</v>
+        <v>-3.6735</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3376</v>
+        <v>-3.3192</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7144</v>
+        <v>-1.7064</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6232</v>
+        <v>-1.6128</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9478</v>
+        <v>-0.9567</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2091</v>
+        <v>-1.2173</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3897</v>
+        <v>-2.3626</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1291</v>
+        <v>-0.4052</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8166</v>
+        <v>-0.8179</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9457</v>
+        <v>0.4127</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.038099999999999</v>
+        <v>3.0236</v>
       </c>
       <c r="E25" t="n">
-        <v>13.8638</v>
+        <v>13.5746</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.8259</v>
+        <v>-10.5511</v>
       </c>
       <c r="G25" t="n">
-        <v>9.7182</v>
+        <v>9.737900000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.184</v>
+        <v>-1.1506</v>
       </c>
       <c r="I25" t="n">
-        <v>10.9021</v>
+        <v>10.8884</v>
       </c>
       <c r="J25" t="n">
-        <v>24.3956</v>
+        <v>24.1863</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0331</v>
+        <v>0.9385000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>23.3624</v>
+        <v>23.2479</v>
       </c>
       <c r="M25" t="n">
-        <v>-14.6775</v>
+        <v>-14.4485</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.2168</v>
+        <v>-2.0892</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.4606</v>
+        <v>-12.3593</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.6708</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.744</v>
+        <v>-14.796</v>
       </c>
       <c r="R25" t="n">
-        <v>9.073499999999999</v>
+        <v>9.105499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.101999999999999</v>
+        <v>-2.1132</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.3722</v>
+        <v>-3.3705</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2701</v>
+        <v>1.2575</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0926</v>
+        <v>1.0893</v>
       </c>
       <c r="W25" t="n">
-        <v>7.5846</v>
+        <v>7.555</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.4918</v>
+        <v>-6.4655</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104549_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104549_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.5549</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104549_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.4655</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
